--- a/data/chinese/P2T3_Chapter10.xlsx
+++ b/data/chinese/P2T3_Chapter10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C44A28-B425-8748-808E-342108E090B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6953CBA8-5DFB-D44A-B4C8-710042CCC450}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="80">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -270,6 +270,10 @@
   </si>
   <si>
     <t>巨人的軀幹變成高大山脈。</t>
+  </si>
+  <si>
+    <t>--</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -356,7 +360,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -376,6 +380,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1416,8 +1426,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="B2" s="6"/>
+    <row r="2" spans="1:2" ht="16">
+      <c r="A2" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" s="6"/>

--- a/data/chinese/P2T3_Chapter10.xlsx
+++ b/data/chinese/P2T3_Chapter10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6953CBA8-5DFB-D44A-B4C8-710042CCC450}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B32DEF-BC95-764A-AC79-9306BC82E2A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -743,7 +743,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="5"/>
     </row>
@@ -758,7 +758,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="5"/>
     </row>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5"/>
     </row>
@@ -788,7 +788,7 @@
         <v>23</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5"/>
     </row>
@@ -803,7 +803,7 @@
         <v>26</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5"/>
     </row>
@@ -818,7 +818,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5"/>
     </row>

--- a/data/chinese/P2T3_Chapter10.xlsx
+++ b/data/chinese/P2T3_Chapter10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Github/ChineseLearning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B32DEF-BC95-764A-AC79-9306BC82E2A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A40B0A-EBD0-4E4A-A140-CE3015827AAB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="79">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -270,10 +270,6 @@
   </si>
   <si>
     <t>巨人的軀幹變成高大山脈。</t>
-  </si>
-  <si>
-    <t>--</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1426,13 +1422,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16">
-      <c r="A2" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>79</v>
-      </c>
+    <row r="2" spans="1:2">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" s="6"/>
